--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-oral.xlsx
@@ -36,27 +36,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 45–90 秒说明 Triton seeded low-memory dropout。</t>
+          <t xml:space="preserve">口述 seeded dropout 的机制与边界。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它保持 inverted dropout 的数学语义，但用 seed 与 global offset 现场重建 keep mask，避免保存完整 mask tensor。
-• [T#B#数学]：保留元素输出 x/(1-p)，丢弃元素输出 0，因此 E(y)=x。
-• [T#B#随机身份]：元素 i 使用 F(seed,i)；global offset 防止不同 program 重复 local-offset 模式。
-• [T#B#复现]：精确输出还依赖 PRNG、p、输入数值语义和逻辑元素到 offset 的映射；元素重排会破坏该映射。
-• [T#B#取舍]：随机状态由 O(N) mask 降为 O(1) seed，并减少 mask 流量，但增加现场 PRNG，所以不能直接推出更快。
-[T#B,!c47f17#边界]：尾部 tl.rand 可以计算无效 offset，但 tensor load/store 必须 mask；不同 seed 也不能保证有限输出一定不同。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它保持 inverted dropout 的期望语义，用 seed 和 global offset 重建随机 mask，以计算换取状态与流量减少。
+• [T#B#数学]：保留时输出x/(1-p)，否则为0；保留概率与逆概率缩放抵消，输出期望仍为x。
+• [T#B#映射与复现]：元素i使用F(seed,i)。同seed还要固定PRNG、offset映射和p才能复现决策，最终输出还依赖输入和数值语义。
+• [T#B#取舍]：避免保存完整mask，但输入/输出流量和缩放仍存在，还增加PRNG；状态更小不能直接证明更快。
+• [T#B#尾部]：由半开区间确定有效lane并满足数量守恒；无效offset可计算随机数，load/store必须mask。
+[T#B,!c47f17#边界]：元素重排可能改变随机身份；状态复杂度降低也不能直接推出运行更快。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说出 inverted scaling 与 E(y)=x；说出 seed 加 global offset 的随机身份；说明精确复现所需条件和重排边界；说明 O(N) mask 到 O(1) seed 的内存取舍；说明尾部 load/store mask 与性能结论边界</t>
+          <t xml:space="preserve">inverted scaling 与期望；global offset 的随机身份；随机数/决策/输出的复现条件；mask 状态与 PRNG 计算取舍；尾部区间、lane 与访存边界</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 综合口述</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-oral.xlsx
@@ -36,22 +36,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">口述 seeded dropout 的机制与边界。</t>
+          <t xml:space="preserve">请用 45–90 秒解释 seeded low-memory dropout：对长度为 N、丢弃概率为 p 的输入向量，如何用 seed 与元素位置重建随机决策，并保证重计算和尾部访存正确？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它保持 inverted dropout 的期望语义，用 seed 和 global offset 重建随机 mask，以计算换取状态与流量减少。
-• [T#B#数学]：保留时输出x/(1-p)，否则为0；保留概率与逆概率缩放抵消，输出期望仍为x。
-• [T#B#映射与复现]：元素i使用F(seed,i)。同seed还要固定PRNG、offset映射和p才能复现决策，最终输出还依赖输入和数值语义。
-• [T#B#取舍]：避免保存完整mask，但输入/输出流量和缩放仍存在，还增加PRNG；状态更小不能直接证明更快。
-• [T#B#尾部]：由半开区间确定有效lane并满足数量守恒；无效offset可计算随机数，load/store必须mask。
-[T#B,!c47f17#边界]：元素重排可能改变随机身份；状态复杂度降低也不能直接推出运行更快。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Seeded dropout 保持 inverted dropout 的数学规则，通过固定的 seed/offset 随机映射重建 mask，以随机数计算换取随机状态和 mask 流量的减少。
+• [T#B#数学规则]：对每个输入 x，保留概率为 1−p：保留时输出 x/(1−p)，否则输出 0。概率与缩放相抵，随机输出的期望仍为 x，其中 0≤p&lt;1。
+• [T#B#随机映射与复现]：全局位置 i 使用 F(seed,i)，不能让不同 program 重复使用从 0 开始的局部编号。要复现决策，还需保持随机数生成实现、元素到 offset 的映射和 p；复现数值输出还要保持输入、dtype 与计算语义。
+• [T#B#内存取舍]：完整 mask 的 O(N) 持久状态被 O(1) seed 替代，省去 mask 物化和读取；输入/输出访问及缩放仍存在，同时增加随机数生成计算，因此不能直接断言更快。
+• [T#B#尾部处理]：以半开区间求出末块范围，用 offset&lt;N 标出有效位置，有效数加无效数等于块长。所有 load/store 都要 mask；无效 offset 的随机数可以计算，因为这不是输入内存访问。
+[T#B,!c47f17#边界]：随机数绑定 offset，不会自动跟随重排后的逻辑元素；相同 seed 不是无条件复现保证。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">inverted scaling 与期望；global offset 的随机身份；随机数/决策/输出的复现条件；mask 状态与 PRNG 计算取舍；尾部区间、lane 与访存边界</t>
+          <t xml:space="preserve">说明保留/清零及 1/(1−p) 缩放为何保持期望；说明 seed 与 global offset 共同决定随机位置；区分随机数、决策与数值输出的复现条件；说明完整 mask 与现场 PRNG 的内存/计算取舍；用半开区间、数量守恒和 load/store mask 解释尾部安全</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-oral.xlsx
@@ -36,22 +36,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用 45–90 秒解释 seeded low-memory dropout：对长度为 N、丢弃概率为 p 的输入向量，如何用 seed 与元素位置重建随机决策，并保证重计算和尾部访存正确？</t>
+          <t xml:space="preserve">面试官问：“在 Triton kernel 里怎样实现 dropout？稍后重算（例如反向传播）时需要和前向完全相同的 keep/drop 决策，但不想把 mask 存下来。”请在 60–90 秒内讲清：保留与缩放规则、随机决策怎样由 seed 和元素位置重建、重算时必须保持什么，以及相对显式保存 mask 的取舍。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：Seeded dropout 保持 inverted dropout 的数学规则，通过固定的 seed/offset 随机映射重建 mask，以随机数计算换取随机状态和 mask 流量的减少。
-• [T#B#数学规则]：对每个输入 x，保留概率为 1−p：保留时输出 x/(1−p)，否则输出 0。概率与缩放相抵，随机输出的期望仍为 x，其中 0≤p&lt;1。
-• [T#B#随机映射与复现]：全局位置 i 使用 F(seed,i)，不能让不同 program 重复使用从 0 开始的局部编号。要复现决策，还需保持随机数生成实现、元素到 offset 的映射和 p；复现数值输出还要保持输入、dtype 与计算语义。
-• [T#B#内存取舍]：完整 mask 的 O(N) 持久状态被 O(1) seed 替代，省去 mask 物化和读取；输入/输出访问及缩放仍存在，同时增加随机数生成计算，因此不能直接断言更快。
-• [T#B#尾部处理]：以半开区间求出末块范围，用 offset&lt;N 标出有效位置，有效数加无效数等于块长。所有 load/store 都要 mask；无效 offset 的随机数可以计算，因为这不是输入内存访问。
-[T#B,!c47f17#边界]：随机数绑定 offset，不会自动跟随重排后的逻辑元素；相同 seed 不是无条件复现保证。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：用 seed 加每个元素的 global offset 现场生成随机数来重建 mask：只需保存一个 seed，代价是每次都要重新计算随机数。
+• [T#B#数学规则]：每个元素以概率 p 丢弃并输出 0，以 1−p 保留并输出 x/(1−p)，所以单元素输出的期望仍是 x。
+• [T#B#随机位置]：元素用 tl.rand(seed, offset) 取随机数，再与 p 比较；offset 必须是 pid×BLOCK+local 的 global offset，若各 program 都传从 0 开始的 local offset，每块会重复同一随机模式。
+• [T#B#重算条件]：要得到同样的随机数，需保持 seed、PRNG 实现和“逻辑元素 → offset”映射；同样的决策还要同一个 p；同样的输出还要输入值、dtype 与数值语义一致。
+• [T#B#取舍]：显式方案要物化、保存并读回 O(N) 的 mask，seeded 方案只存 O(1) 的 seed；但输入输出访问和缩放仍在，还多了 PRNG 计算，所以不能直接断言更快。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明保留/清零及 1/(1−p) 缩放为何保持期望；说明 seed 与 global offset 共同决定随机位置；区分随机数、决策与数值输出的复现条件；说明完整 mask 与现场 PRNG 的内存/计算取舍；用半开区间、数量守恒和 load/store mask 解释尾部安全</t>
+          <t xml:space="preserve">说明以 1−p 的概率保留并乘 1/(1−p)，使单元素期望仍为 x；说明 tl.rand 要用 seed 和 global offset，local offset 会让各块重复同一随机模式；按随机数、决策、输出三层说出重算时要保持的条件；说明省掉 O(N) mask 的物化、保存与读取，换来 PRNG 计算，因此不能直接断言更快</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
